--- a/data/contatos.xlsx
+++ b/data/contatos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfsoa\Desktop\Nutri_Hospital\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9276D6F5-8853-4FBF-B064-F423A671D12D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F0EF90-F159-4CEF-B19B-683B249E4B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="101460" yWindow="4395" windowWidth="12495" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="76680" yWindow="165" windowWidth="38640" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="contatos" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="139">
-  <si>
-    <t>id_contato</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="275">
   <si>
     <t>nome_contato</t>
   </si>
@@ -64,9 +61,6 @@
     <t>COMPRAS</t>
   </si>
   <si>
-    <t>37 3359-7230</t>
-  </si>
-  <si>
     <t>SANTA CASA DE BOM DESPACHO</t>
   </si>
   <si>
@@ -133,9 +127,6 @@
     <t>GUSTAVO</t>
   </si>
   <si>
-    <t>035 99955-6059</t>
-  </si>
-  <si>
     <t>HOSPITAL SANTA LÚCIA</t>
   </si>
   <si>
@@ -433,10 +424,427 @@
     <t>037 99902-1311</t>
   </si>
   <si>
-    <t>id_hospital</t>
-  </si>
-  <si>
-    <t>nome_hospital</t>
+    <t>id</t>
+  </si>
+  <si>
+    <t>hospital_id</t>
+  </si>
+  <si>
+    <t>hospital_nome</t>
+  </si>
+  <si>
+    <t>(37)9 9999-1578</t>
+  </si>
+  <si>
+    <t>(35) 99955-6059</t>
+  </si>
+  <si>
+    <t>COMPLEXO HOSPITALAR IMACULADA CONCEIÇÃO</t>
+  </si>
+  <si>
+    <t>Sem nome</t>
+  </si>
+  <si>
+    <t>(38) 3729-1211</t>
+  </si>
+  <si>
+    <t>HOSPITAL SÃO VICENTE DE PAULA</t>
+  </si>
+  <si>
+    <t>(37) 3541-1144</t>
+  </si>
+  <si>
+    <t>HOSPITAL MUNICIPAL SÃO JOSÉ</t>
+  </si>
+  <si>
+    <t>(37) 3351-1467</t>
+  </si>
+  <si>
+    <t>HOSPITAL NOSSA SENHORA DO BRASIL</t>
+  </si>
+  <si>
+    <t>(37) 3417-0241</t>
+  </si>
+  <si>
+    <t>HOSPITAL REGIONAL DE BARBACENA DOUTOR JOSÉ AMÉRICO</t>
+  </si>
+  <si>
+    <t>(37) 3339-1600</t>
+  </si>
+  <si>
+    <t>HOSPITAL IBIAPABA</t>
+  </si>
+  <si>
+    <t>(32) 3339-3500</t>
+  </si>
+  <si>
+    <t>INSTITUTO NOSSA SENHORA DO CARMO</t>
+  </si>
+  <si>
+    <t>(32) 3359-3950</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE BOM SUCESSO</t>
+  </si>
+  <si>
+    <t>(35) 9 9976-0155</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE CAMPO BELO</t>
+  </si>
+  <si>
+    <t>LUANA</t>
+  </si>
+  <si>
+    <t>NUTRICIONISTA RT</t>
+  </si>
+  <si>
+    <t>(35) 99844-6134</t>
+  </si>
+  <si>
+    <t>HOSPITAL SÃO LUCAS</t>
+  </si>
+  <si>
+    <t>(35) 3831-1038</t>
+  </si>
+  <si>
+    <t>HOSPITAL OLINTO FERREIRA DINIZ</t>
+  </si>
+  <si>
+    <t>(35) 3338-1152</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE MISERICÓRDIA NOSSA SENHORA DO CARMO</t>
+  </si>
+  <si>
+    <t>(37) 3333-1589</t>
+  </si>
+  <si>
+    <t>HOSPITAL SÃO VICENTE DE PAULO</t>
+  </si>
+  <si>
+    <t>(35) 3327-1077</t>
+  </si>
+  <si>
+    <t>HOSPITAL MUNICIPAL SANTO ANTÔNIO DE CRISTAIS</t>
+  </si>
+  <si>
+    <t>(35) 3835-2411</t>
+  </si>
+  <si>
+    <t>HOSPITAL SANTO ANTÔNIO</t>
+  </si>
+  <si>
+    <t>FERNANDA</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>(38)99102-9473</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE MISERICÓRDIA DOUTOR ZACARIAS</t>
+  </si>
+  <si>
+    <t>(37) 3551-1200</t>
+  </si>
+  <si>
+    <t>HOSPITAL MUNICIPAL DE ESTRELA DO INDAIÁ</t>
+  </si>
+  <si>
+    <t>(37) 3553-1220</t>
+  </si>
+  <si>
+    <t>HFOR HOSPITAL DE FORMIGA (HOSPITAL DIA)</t>
+  </si>
+  <si>
+    <t>(37) 3321-2200</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE MISERICÓRDIA DE IBERTIOGA (MONUMENTO AS MÃES)</t>
+  </si>
+  <si>
+    <t>(32) 3347-1290</t>
+  </si>
+  <si>
+    <t>HOSPITAL E MATERNIDADE REGIONAL DE IBIRITÉ</t>
+  </si>
+  <si>
+    <t>(31) 2010-3700</t>
+  </si>
+  <si>
+    <t>HOSPITAL ICSMEP</t>
+  </si>
+  <si>
+    <t>(31) 3512-4400</t>
+  </si>
+  <si>
+    <t>HOSPITAL MUNICIPAL SÃO FRANCISCO</t>
+  </si>
+  <si>
+    <t>(37) 3353-2400</t>
+  </si>
+  <si>
+    <t>HOSPITAL SÃO VICENTE DE PAULO ITABIRITO (SÃO CAMILO)</t>
+  </si>
+  <si>
+    <t>(31) 3562-4303</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE ITAGUARA</t>
+  </si>
+  <si>
+    <t>(31) 3184-1666</t>
+  </si>
+  <si>
+    <t>(32) 3338-1255</t>
+  </si>
+  <si>
+    <t>HOSPITAL DOUTOR ODILON ANDRADE</t>
+  </si>
+  <si>
+    <t>(37) 3524-1217</t>
+  </si>
+  <si>
+    <t>HOSPITAL SANTA TEREZINHA</t>
+  </si>
+  <si>
+    <t>(31) 3523-2700</t>
+  </si>
+  <si>
+    <t>HOSPITAL PROFESSOR BASÍLIO MOEMA</t>
+  </si>
+  <si>
+    <t>(37) 3525-0206</t>
+  </si>
+  <si>
+    <t>HOSPITAL CASA DE CARIDADE SÃO SEBASTIÃO</t>
+  </si>
+  <si>
+    <t>(37) 3755-1231</t>
+  </si>
+  <si>
+    <t>HOSPITAL MUNICIPAL SANTO ANTÔNIO</t>
+  </si>
+  <si>
+    <t>(35) 3842-1212</t>
+  </si>
+  <si>
+    <t>HOSPITAL NOSSA SENHORA DE LOURDES</t>
+  </si>
+  <si>
+    <t>(31) 3589-1332</t>
+  </si>
+  <si>
+    <t>HOSPITAL MATER DEI NOVA LIMA</t>
+  </si>
+  <si>
+    <t>(31) 3339-9800</t>
+  </si>
+  <si>
+    <t>HOSPITAL SANTA MÔNICA NOVA SERRANA (HAPVIDA NOTREDAME INTERMÉDICA)</t>
+  </si>
+  <si>
+    <t>(37) 2102-5600</t>
+  </si>
+  <si>
+    <t>HOSPITAL SÃO JOSÉ DE NOVA SERRANA</t>
+  </si>
+  <si>
+    <t>HOSPITAL MUNICIPAL REGINA VILELA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>(37) 3323-1222</t>
+  </si>
+  <si>
+    <t>HOSPITAL MUNICIPAL PADRE LIBÉRIO (HOSPITAL DIA)</t>
+  </si>
+  <si>
+    <t>(37) 3233-5830</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE MISERICÓRDIA DE PASSA TEMPO (HOSPITAL SÃO GABRIEL)</t>
+  </si>
+  <si>
+    <t>(37) 3335-1250</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE MISERICÓRDIA DE PERDÕES</t>
+  </si>
+  <si>
+    <t>(35) 3864-1114</t>
+  </si>
+  <si>
+    <t>PEQUENO HOSPITAL SANTA MARIA DE ANTÔNIO CARLOS</t>
+  </si>
+  <si>
+    <t>(32) 3335-1233</t>
+  </si>
+  <si>
+    <t>PEQUENO HOSPITAL NOSSA SENHORA DA PIEDADE</t>
+  </si>
+  <si>
+    <t>SANTA CASA MUNICIPAL DE SAÚDE DE PIMENTA</t>
+  </si>
+  <si>
+    <t>(37) 3324-1519</t>
+  </si>
+  <si>
+    <t>HOSPITAL JOAQUIM PINTO LARA (CENTRO DE SAÚDE)</t>
+  </si>
+  <si>
+    <t>(37) 3334-1160</t>
+  </si>
+  <si>
+    <t>IRMANDADE DA SANTA CASA DE MISERICÓRDIA DE PITANGUI</t>
+  </si>
+  <si>
+    <t>(37) 3271-4012</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE MISERICÓRDIA DE PIUMHI</t>
+  </si>
+  <si>
+    <t>(37) 3371-9500</t>
+  </si>
+  <si>
+    <t>HOSPITAL DIA DE PIUMHI</t>
+  </si>
+  <si>
+    <t>(37) 3412-0075</t>
+  </si>
+  <si>
+    <t>HOSPITAL SANTA CASA DE MISERICÓRDIA DE POMPÉU</t>
+  </si>
+  <si>
+    <t>(37) 3523-1222</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE MISERICÓRDIA DA PARÓQUIA DE PRADOS</t>
+  </si>
+  <si>
+    <t>(32) 3353-6399</t>
+  </si>
+  <si>
+    <t>HOSPITAL NOSSA SENHORA DO ROSÁRIO</t>
+  </si>
+  <si>
+    <t>(32) 3354-1211</t>
+  </si>
+  <si>
+    <t>HOSPITAL MUNICIPAL SÃO JUDAS TADEU</t>
+  </si>
+  <si>
+    <t>(31) 3627-5238</t>
+  </si>
+  <si>
+    <t>HOSPITAL MUNICIPAL DE RIBEIRÃO VERMELHO</t>
+  </si>
+  <si>
+    <t>(35) 3867-1230</t>
+  </si>
+  <si>
+    <t>HOSPITAL MUNICIPAL PEDRO GIANNETTI</t>
+  </si>
+  <si>
+    <t>(31) 3545-1287</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE SABARÁ</t>
+  </si>
+  <si>
+    <t>(31) 3671-5444</t>
+  </si>
+  <si>
+    <t>HOSPITAL MUNICIPAL MADALENA PARRILLO CALIXTO</t>
+  </si>
+  <si>
+    <t>(31) 3649-6867</t>
+  </si>
+  <si>
+    <t>HOSPITAL DE SÃO JOÃO DE DEUS DE SANTA LUZIA</t>
+  </si>
+  <si>
+    <t>(31) 3100-5100</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE SANTO ANTÔNIO DO AMPARO (HOSPITAL SÃO SEBASTIÃO)</t>
+  </si>
+  <si>
+    <t>(35) 3863-2710</t>
+  </si>
+  <si>
+    <t>Santo Antônio do Monte: Santa Casa de Misericórdia de Santo Antônio do Monte</t>
+  </si>
+  <si>
+    <t>(37) 3281-8900</t>
+  </si>
+  <si>
+    <t>HOSPITAL DE NOSSA SENHORA DAS MERCÊS</t>
+  </si>
+  <si>
+    <t>(32) 3379-2800</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE MISERICÓRDIA DE SÃO JOÃO DEL REI</t>
+  </si>
+  <si>
+    <t>(32) 3379-2000</t>
+  </si>
+  <si>
+    <t>HOSPITAL SANTA MARTA</t>
+  </si>
+  <si>
+    <t>(37) 3433-1593</t>
+  </si>
+  <si>
+    <t>(32) 3376-1232</t>
+  </si>
+  <si>
+    <t>(35) 3323-1295</t>
+  </si>
+  <si>
+    <t>HOSPITAL SÃO FRANCISCO</t>
+  </si>
+  <si>
+    <t>(38) 3754-1256</t>
+  </si>
+  <si>
+    <t>FUNDAÇÃO VESPASIANENSE DE SAÚDE (HOSPITAL DE DEUS)</t>
+  </si>
+  <si>
+    <t>(31) 3621-0853</t>
+  </si>
+  <si>
+    <t>JÉSSICA</t>
+  </si>
+  <si>
+    <t>(37) 9 9846-9038</t>
+  </si>
+  <si>
+    <t>HOSPITAL SÃO BENTO MENNI</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>(37) 99843-6750</t>
+  </si>
+  <si>
+    <t>CASA DE SAÚDE SÃO FRANCISCO DE ASSIS</t>
+  </si>
+  <si>
+    <t>RT NUTRI CLÍNICA</t>
+  </si>
+  <si>
+    <t>(37)99903-0982</t>
+  </si>
+  <si>
+    <t>LETÍCIA</t>
+  </si>
+  <si>
+    <t>(35)99962-5287</t>
   </si>
 </sst>
 </file>
@@ -776,1061 +1184,2229 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="18" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>2</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>4</v>
+        <v>158</v>
       </c>
       <c r="B2">
         <v>4</v>
       </c>
       <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>5</v>
+        <v>159</v>
       </c>
       <c r="B3">
         <v>5</v>
       </c>
       <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>6</v>
+        <v>160</v>
       </c>
       <c r="B4">
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>7</v>
+        <v>161</v>
       </c>
       <c r="B5">
         <v>6</v>
       </c>
       <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
         <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>8</v>
+        <v>162</v>
       </c>
       <c r="B6">
         <v>7</v>
       </c>
       <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
         <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>9</v>
+        <v>163</v>
       </c>
       <c r="B7">
         <v>8</v>
       </c>
       <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
         <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>10</v>
+        <v>164</v>
       </c>
       <c r="B8">
         <v>9</v>
       </c>
       <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
         <v>24</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>11</v>
+        <v>165</v>
       </c>
       <c r="B9">
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>12</v>
+        <v>166</v>
       </c>
       <c r="B10">
         <v>10</v>
       </c>
       <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
         <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>13</v>
+        <v>167</v>
       </c>
       <c r="B11">
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>14</v>
+        <v>168</v>
       </c>
       <c r="B12">
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>15</v>
+        <v>169</v>
       </c>
       <c r="B13">
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="B14">
         <v>12</v>
       </c>
       <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s">
         <v>38</v>
       </c>
-      <c r="D14" t="s">
-        <v>41</v>
-      </c>
       <c r="E14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>17</v>
+        <v>171</v>
       </c>
       <c r="B15">
         <v>13</v>
       </c>
       <c r="C15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" t="s">
         <v>43</v>
-      </c>
-      <c r="D15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>18</v>
+        <v>172</v>
       </c>
       <c r="B16">
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>19</v>
+        <v>173</v>
       </c>
       <c r="B17">
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="B18">
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="B19">
         <v>14</v>
       </c>
       <c r="C19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" t="s">
         <v>53</v>
       </c>
-      <c r="D19" t="s">
-        <v>56</v>
-      </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>22</v>
+        <v>176</v>
       </c>
       <c r="B20">
         <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>23</v>
+        <v>177</v>
       </c>
       <c r="B21">
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>24</v>
+        <v>178</v>
       </c>
       <c r="B22">
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F22" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>25</v>
+        <v>179</v>
       </c>
       <c r="B23">
         <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D23" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>26</v>
+        <v>180</v>
       </c>
       <c r="B24">
         <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>27</v>
+        <v>181</v>
       </c>
       <c r="B25">
         <v>15</v>
       </c>
       <c r="C25" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" t="s">
         <v>66</v>
       </c>
-      <c r="D25" t="s">
-        <v>69</v>
-      </c>
       <c r="E25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F25" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>28</v>
+        <v>182</v>
       </c>
       <c r="B26">
         <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E26" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F26" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>29</v>
+        <v>183</v>
       </c>
       <c r="B27">
         <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E27" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="B28">
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>31</v>
+        <v>185</v>
       </c>
       <c r="B29">
         <v>16</v>
       </c>
       <c r="C29" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" t="s">
         <v>75</v>
       </c>
-      <c r="D29" t="s">
-        <v>78</v>
-      </c>
       <c r="E29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>32</v>
+        <v>186</v>
       </c>
       <c r="B30">
         <v>17</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E30" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F30" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>33</v>
+        <v>187</v>
       </c>
       <c r="B31">
         <v>17</v>
       </c>
       <c r="C31" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" t="s">
         <v>80</v>
       </c>
-      <c r="D31" t="s">
-        <v>83</v>
-      </c>
       <c r="E31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="B32">
         <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D32" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="B33">
         <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D33" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>36</v>
+        <v>190</v>
       </c>
       <c r="B34">
         <v>19</v>
       </c>
       <c r="C34" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D34" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>37</v>
+        <v>191</v>
       </c>
       <c r="B35">
         <v>19</v>
       </c>
       <c r="C35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
         <v>87</v>
-      </c>
-      <c r="D35" t="s">
-        <v>89</v>
-      </c>
-      <c r="E35" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>38</v>
+        <v>192</v>
       </c>
       <c r="B36">
         <v>19</v>
       </c>
       <c r="C36" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E36" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>39</v>
+        <v>193</v>
       </c>
       <c r="B37">
         <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D37" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F37" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>40</v>
+        <v>194</v>
       </c>
       <c r="B38">
         <v>20</v>
       </c>
       <c r="C38" t="s">
+        <v>90</v>
+      </c>
+      <c r="D38" t="s">
         <v>93</v>
       </c>
-      <c r="D38" t="s">
-        <v>96</v>
-      </c>
       <c r="E38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F38" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>41</v>
+        <v>195</v>
       </c>
       <c r="B39">
         <v>21</v>
       </c>
       <c r="C39" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D39" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F39" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>42</v>
+        <v>196</v>
       </c>
       <c r="B40">
         <v>21</v>
       </c>
       <c r="C40" t="s">
+        <v>95</v>
+      </c>
+      <c r="D40" t="s">
         <v>98</v>
       </c>
-      <c r="D40" t="s">
-        <v>101</v>
-      </c>
       <c r="E40" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F40" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>43</v>
+        <v>197</v>
       </c>
       <c r="B41">
         <v>22</v>
       </c>
       <c r="C41" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D41" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F41" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>44</v>
+        <v>198</v>
       </c>
       <c r="B42">
         <v>22</v>
       </c>
       <c r="C42" t="s">
+        <v>100</v>
+      </c>
+      <c r="D42" t="s">
         <v>103</v>
       </c>
-      <c r="D42" t="s">
-        <v>106</v>
-      </c>
       <c r="E42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F42" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>45</v>
+        <v>199</v>
       </c>
       <c r="B43">
         <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D43" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F43" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>46</v>
+        <v>200</v>
       </c>
       <c r="B44">
         <v>23</v>
       </c>
       <c r="C44" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D44" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F44" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>47</v>
+        <v>201</v>
       </c>
       <c r="B45">
         <v>24</v>
       </c>
       <c r="C45" t="s">
+        <v>110</v>
+      </c>
+      <c r="D45" t="s">
+        <v>111</v>
+      </c>
+      <c r="E45" t="s">
+        <v>112</v>
+      </c>
+      <c r="F45" t="s">
         <v>113</v>
-      </c>
-      <c r="D45" t="s">
-        <v>114</v>
-      </c>
-      <c r="E45" t="s">
-        <v>115</v>
-      </c>
-      <c r="F45" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="B46">
         <v>24</v>
       </c>
       <c r="C46" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D46" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E46" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F46" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>49</v>
+        <v>203</v>
       </c>
       <c r="B47">
         <v>24</v>
       </c>
       <c r="C47" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D47" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E47" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F47" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>50</v>
+        <v>204</v>
       </c>
       <c r="B48">
         <v>24</v>
       </c>
       <c r="C48" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D48" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F48" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>51</v>
+        <v>205</v>
       </c>
       <c r="B49">
         <v>25</v>
       </c>
       <c r="C49" t="s">
+        <v>122</v>
+      </c>
+      <c r="D49" t="s">
+        <v>123</v>
+      </c>
+      <c r="E49" t="s">
+        <v>124</v>
+      </c>
+      <c r="F49" t="s">
         <v>125</v>
-      </c>
-      <c r="D49" t="s">
-        <v>126</v>
-      </c>
-      <c r="E49" t="s">
-        <v>127</v>
-      </c>
-      <c r="F49" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>52</v>
+        <v>206</v>
       </c>
       <c r="B50">
         <v>25</v>
       </c>
       <c r="C50" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D50" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E50" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F50" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>53</v>
+        <v>207</v>
       </c>
       <c r="B51">
         <v>25</v>
       </c>
       <c r="C51" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D51" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E51" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>54</v>
+        <v>208</v>
       </c>
       <c r="B52">
         <v>26</v>
       </c>
       <c r="C52" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D52" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E52" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F52" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>55</v>
+        <v>209</v>
       </c>
       <c r="B53">
         <v>26</v>
       </c>
       <c r="C53" t="s">
+        <v>129</v>
+      </c>
+      <c r="D53" t="s">
         <v>132</v>
       </c>
-      <c r="D53" t="s">
-        <v>135</v>
-      </c>
       <c r="E53" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F53" t="s">
-        <v>136</v>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>210</v>
+      </c>
+      <c r="B54">
+        <v>41</v>
+      </c>
+      <c r="C54" t="s">
+        <v>139</v>
+      </c>
+      <c r="D54" t="s">
+        <v>140</v>
+      </c>
+      <c r="F54" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>211</v>
+      </c>
+      <c r="B55">
+        <v>27</v>
+      </c>
+      <c r="C55" t="s">
+        <v>142</v>
+      </c>
+      <c r="D55" t="s">
+        <v>140</v>
+      </c>
+      <c r="F55" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>213</v>
+      </c>
+      <c r="B56">
+        <v>29</v>
+      </c>
+      <c r="C56" t="s">
+        <v>144</v>
+      </c>
+      <c r="D56" t="s">
+        <v>140</v>
+      </c>
+      <c r="F56" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>214</v>
+      </c>
+      <c r="B57">
+        <v>30</v>
+      </c>
+      <c r="C57" t="s">
+        <v>146</v>
+      </c>
+      <c r="D57" t="s">
+        <v>140</v>
+      </c>
+      <c r="F57" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>217</v>
+      </c>
+      <c r="B58">
+        <v>31</v>
+      </c>
+      <c r="C58" t="s">
+        <v>148</v>
+      </c>
+      <c r="D58" t="s">
+        <v>140</v>
+      </c>
+      <c r="F58" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>218</v>
+      </c>
+      <c r="B59">
+        <v>32</v>
+      </c>
+      <c r="C59" t="s">
+        <v>150</v>
+      </c>
+      <c r="D59" t="s">
+        <v>140</v>
+      </c>
+      <c r="F59" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>219</v>
+      </c>
+      <c r="B60">
+        <v>33</v>
+      </c>
+      <c r="C60" t="s">
+        <v>152</v>
+      </c>
+      <c r="D60" t="s">
+        <v>140</v>
+      </c>
+      <c r="F60" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>220</v>
+      </c>
+      <c r="B61">
+        <v>34</v>
+      </c>
+      <c r="C61" t="s">
+        <v>154</v>
+      </c>
+      <c r="D61" t="s">
+        <v>140</v>
+      </c>
+      <c r="F61" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>221</v>
+      </c>
+      <c r="B62">
+        <v>35</v>
+      </c>
+      <c r="C62" t="s">
+        <v>156</v>
+      </c>
+      <c r="D62" t="s">
+        <v>157</v>
+      </c>
+      <c r="E62" t="s">
+        <v>158</v>
+      </c>
+      <c r="F62" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>222</v>
+      </c>
+      <c r="B63">
+        <v>36</v>
+      </c>
+      <c r="C63" t="s">
+        <v>160</v>
+      </c>
+      <c r="D63" t="s">
+        <v>140</v>
+      </c>
+      <c r="F63" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>223</v>
+      </c>
+      <c r="B64">
+        <v>37</v>
+      </c>
+      <c r="C64" t="s">
+        <v>162</v>
+      </c>
+      <c r="D64" t="s">
+        <v>140</v>
+      </c>
+      <c r="F64" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>224</v>
+      </c>
+      <c r="B65">
+        <v>38</v>
+      </c>
+      <c r="C65" t="s">
+        <v>164</v>
+      </c>
+      <c r="D65" t="s">
+        <v>140</v>
+      </c>
+      <c r="F65" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>225</v>
+      </c>
+      <c r="B66">
+        <v>39</v>
+      </c>
+      <c r="C66" t="s">
+        <v>166</v>
+      </c>
+      <c r="D66" t="s">
+        <v>140</v>
+      </c>
+      <c r="F66" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>226</v>
+      </c>
+      <c r="B67">
+        <v>40</v>
+      </c>
+      <c r="C67" t="s">
+        <v>168</v>
+      </c>
+      <c r="D67" t="s">
+        <v>140</v>
+      </c>
+      <c r="F67" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>227</v>
+      </c>
+      <c r="B68">
+        <v>42</v>
+      </c>
+      <c r="C68" t="s">
+        <v>170</v>
+      </c>
+      <c r="D68" t="s">
+        <v>171</v>
+      </c>
+      <c r="E68" t="s">
+        <v>172</v>
+      </c>
+      <c r="F68" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>228</v>
+      </c>
+      <c r="B69">
+        <v>43</v>
+      </c>
+      <c r="C69" t="s">
+        <v>174</v>
+      </c>
+      <c r="D69" t="s">
+        <v>140</v>
+      </c>
+      <c r="F69" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>229</v>
+      </c>
+      <c r="B70">
+        <v>44</v>
+      </c>
+      <c r="C70" t="s">
+        <v>176</v>
+      </c>
+      <c r="D70" t="s">
+        <v>140</v>
+      </c>
+      <c r="F70" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>230</v>
+      </c>
+      <c r="B71">
+        <v>46</v>
+      </c>
+      <c r="C71" t="s">
+        <v>178</v>
+      </c>
+      <c r="D71" t="s">
+        <v>140</v>
+      </c>
+      <c r="F71" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>231</v>
+      </c>
+      <c r="B72">
+        <v>47</v>
+      </c>
+      <c r="C72" t="s">
+        <v>180</v>
+      </c>
+      <c r="D72" t="s">
+        <v>140</v>
+      </c>
+      <c r="F72" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>232</v>
+      </c>
+      <c r="B73">
+        <v>48</v>
+      </c>
+      <c r="C73" t="s">
+        <v>182</v>
+      </c>
+      <c r="D73" t="s">
+        <v>140</v>
+      </c>
+      <c r="F73" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>233</v>
+      </c>
+      <c r="B74">
+        <v>49</v>
+      </c>
+      <c r="C74" t="s">
+        <v>184</v>
+      </c>
+      <c r="D74" t="s">
+        <v>140</v>
+      </c>
+      <c r="F74" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>234</v>
+      </c>
+      <c r="B75">
+        <v>50</v>
+      </c>
+      <c r="C75" t="s">
+        <v>186</v>
+      </c>
+      <c r="D75" t="s">
+        <v>140</v>
+      </c>
+      <c r="F75" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>235</v>
+      </c>
+      <c r="B76">
+        <v>51</v>
+      </c>
+      <c r="C76" t="s">
+        <v>188</v>
+      </c>
+      <c r="D76" t="s">
+        <v>140</v>
+      </c>
+      <c r="F76" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>236</v>
+      </c>
+      <c r="B77">
+        <v>52</v>
+      </c>
+      <c r="C77" t="s">
+        <v>190</v>
+      </c>
+      <c r="D77" t="s">
+        <v>140</v>
+      </c>
+      <c r="F77" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>237</v>
+      </c>
+      <c r="B78">
+        <v>53</v>
+      </c>
+      <c r="C78" t="s">
+        <v>63</v>
+      </c>
+      <c r="D78" t="s">
+        <v>140</v>
+      </c>
+      <c r="F78" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>238</v>
+      </c>
+      <c r="B79">
+        <v>54</v>
+      </c>
+      <c r="C79" t="s">
+        <v>193</v>
+      </c>
+      <c r="D79" t="s">
+        <v>140</v>
+      </c>
+      <c r="F79" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>239</v>
+      </c>
+      <c r="B80">
+        <v>55</v>
+      </c>
+      <c r="C80" t="s">
+        <v>195</v>
+      </c>
+      <c r="D80" t="s">
+        <v>140</v>
+      </c>
+      <c r="F80" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>240</v>
+      </c>
+      <c r="B81">
+        <v>56</v>
+      </c>
+      <c r="C81" t="s">
+        <v>197</v>
+      </c>
+      <c r="D81" t="s">
+        <v>140</v>
+      </c>
+      <c r="F81" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>241</v>
+      </c>
+      <c r="B82">
+        <v>57</v>
+      </c>
+      <c r="C82" t="s">
+        <v>199</v>
+      </c>
+      <c r="D82" t="s">
+        <v>140</v>
+      </c>
+      <c r="F82" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>242</v>
+      </c>
+      <c r="B83">
+        <v>58</v>
+      </c>
+      <c r="C83" t="s">
+        <v>201</v>
+      </c>
+      <c r="D83" t="s">
+        <v>140</v>
+      </c>
+      <c r="F83" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>243</v>
+      </c>
+      <c r="B84">
+        <v>59</v>
+      </c>
+      <c r="C84" t="s">
+        <v>203</v>
+      </c>
+      <c r="D84" t="s">
+        <v>140</v>
+      </c>
+      <c r="F84" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>244</v>
+      </c>
+      <c r="B85">
+        <v>60</v>
+      </c>
+      <c r="C85" t="s">
+        <v>205</v>
+      </c>
+      <c r="D85" t="s">
+        <v>140</v>
+      </c>
+      <c r="F85" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>245</v>
+      </c>
+      <c r="B86">
+        <v>61</v>
+      </c>
+      <c r="C86" t="s">
+        <v>207</v>
+      </c>
+      <c r="D86" t="s">
+        <v>140</v>
+      </c>
+      <c r="F86" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>246</v>
+      </c>
+      <c r="B87">
+        <v>62</v>
+      </c>
+      <c r="C87" t="s">
+        <v>209</v>
+      </c>
+      <c r="D87" t="s">
+        <v>140</v>
+      </c>
+      <c r="F87" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>247</v>
+      </c>
+      <c r="B88">
+        <v>63</v>
+      </c>
+      <c r="C88" t="s">
+        <v>210</v>
+      </c>
+      <c r="D88" t="s">
+        <v>140</v>
+      </c>
+      <c r="F88" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>248</v>
+      </c>
+      <c r="B89">
+        <v>64</v>
+      </c>
+      <c r="C89" t="s">
+        <v>212</v>
+      </c>
+      <c r="D89" t="s">
+        <v>140</v>
+      </c>
+      <c r="F89" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>249</v>
+      </c>
+      <c r="B90">
+        <v>65</v>
+      </c>
+      <c r="C90" t="s">
+        <v>214</v>
+      </c>
+      <c r="D90" t="s">
+        <v>140</v>
+      </c>
+      <c r="F90" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>250</v>
+      </c>
+      <c r="B91">
+        <v>66</v>
+      </c>
+      <c r="C91" t="s">
+        <v>216</v>
+      </c>
+      <c r="D91" t="s">
+        <v>140</v>
+      </c>
+      <c r="F91" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>251</v>
+      </c>
+      <c r="B92">
+        <v>28</v>
+      </c>
+      <c r="C92" t="s">
+        <v>218</v>
+      </c>
+      <c r="D92" t="s">
+        <v>140</v>
+      </c>
+      <c r="F92" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>252</v>
+      </c>
+      <c r="B93">
+        <v>67</v>
+      </c>
+      <c r="C93" t="s">
+        <v>220</v>
+      </c>
+      <c r="D93" t="s">
+        <v>140</v>
+      </c>
+      <c r="F93" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>253</v>
+      </c>
+      <c r="B94">
+        <v>68</v>
+      </c>
+      <c r="C94" t="s">
+        <v>221</v>
+      </c>
+      <c r="D94" t="s">
+        <v>140</v>
+      </c>
+      <c r="F94" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>254</v>
+      </c>
+      <c r="B95">
+        <v>69</v>
+      </c>
+      <c r="C95" t="s">
+        <v>223</v>
+      </c>
+      <c r="D95" t="s">
+        <v>140</v>
+      </c>
+      <c r="F95" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>255</v>
+      </c>
+      <c r="B96">
+        <v>70</v>
+      </c>
+      <c r="C96" t="s">
+        <v>225</v>
+      </c>
+      <c r="D96" t="s">
+        <v>140</v>
+      </c>
+      <c r="F96" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>256</v>
+      </c>
+      <c r="B97">
+        <v>71</v>
+      </c>
+      <c r="C97" t="s">
+        <v>227</v>
+      </c>
+      <c r="D97" t="s">
+        <v>140</v>
+      </c>
+      <c r="F97" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>257</v>
+      </c>
+      <c r="B98">
+        <v>72</v>
+      </c>
+      <c r="C98" t="s">
+        <v>229</v>
+      </c>
+      <c r="D98" t="s">
+        <v>140</v>
+      </c>
+      <c r="F98" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>258</v>
+      </c>
+      <c r="B99">
+        <v>73</v>
+      </c>
+      <c r="C99" t="s">
+        <v>231</v>
+      </c>
+      <c r="D99" t="s">
+        <v>140</v>
+      </c>
+      <c r="F99" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>259</v>
+      </c>
+      <c r="B100">
+        <v>74</v>
+      </c>
+      <c r="C100" t="s">
+        <v>233</v>
+      </c>
+      <c r="D100" t="s">
+        <v>140</v>
+      </c>
+      <c r="F100" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>260</v>
+      </c>
+      <c r="B101">
+        <v>75</v>
+      </c>
+      <c r="C101" t="s">
+        <v>235</v>
+      </c>
+      <c r="D101" t="s">
+        <v>140</v>
+      </c>
+      <c r="F101" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>261</v>
+      </c>
+      <c r="B102">
+        <v>76</v>
+      </c>
+      <c r="C102" t="s">
+        <v>237</v>
+      </c>
+      <c r="D102" t="s">
+        <v>140</v>
+      </c>
+      <c r="F102" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>262</v>
+      </c>
+      <c r="B103">
+        <v>77</v>
+      </c>
+      <c r="C103" t="s">
+        <v>239</v>
+      </c>
+      <c r="D103" t="s">
+        <v>140</v>
+      </c>
+      <c r="F103" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>263</v>
+      </c>
+      <c r="B104">
+        <v>78</v>
+      </c>
+      <c r="C104" t="s">
+        <v>241</v>
+      </c>
+      <c r="D104" t="s">
+        <v>140</v>
+      </c>
+      <c r="F104" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>264</v>
+      </c>
+      <c r="B105">
+        <v>78</v>
+      </c>
+      <c r="C105" t="s">
+        <v>241</v>
+      </c>
+      <c r="D105" t="s">
+        <v>140</v>
+      </c>
+      <c r="F105" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>265</v>
+      </c>
+      <c r="B106">
+        <v>79</v>
+      </c>
+      <c r="C106" t="s">
+        <v>243</v>
+      </c>
+      <c r="D106" t="s">
+        <v>140</v>
+      </c>
+      <c r="F106" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>266</v>
+      </c>
+      <c r="B107">
+        <v>80</v>
+      </c>
+      <c r="C107" t="s">
+        <v>245</v>
+      </c>
+      <c r="D107" t="s">
+        <v>140</v>
+      </c>
+      <c r="F107" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>267</v>
+      </c>
+      <c r="B108">
+        <v>81</v>
+      </c>
+      <c r="C108" t="s">
+        <v>247</v>
+      </c>
+      <c r="D108" t="s">
+        <v>140</v>
+      </c>
+      <c r="F108" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>269</v>
+      </c>
+      <c r="B109">
+        <v>82</v>
+      </c>
+      <c r="C109" t="s">
+        <v>249</v>
+      </c>
+      <c r="D109" t="s">
+        <v>140</v>
+      </c>
+      <c r="F109" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>270</v>
+      </c>
+      <c r="B110">
+        <v>83</v>
+      </c>
+      <c r="C110" t="s">
+        <v>251</v>
+      </c>
+      <c r="D110" t="s">
+        <v>140</v>
+      </c>
+      <c r="F110" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>271</v>
+      </c>
+      <c r="B111">
+        <v>84</v>
+      </c>
+      <c r="C111" t="s">
+        <v>253</v>
+      </c>
+      <c r="D111" t="s">
+        <v>140</v>
+      </c>
+      <c r="F111" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>272</v>
+      </c>
+      <c r="B112">
+        <v>85</v>
+      </c>
+      <c r="C112" t="s">
+        <v>255</v>
+      </c>
+      <c r="D112" t="s">
+        <v>140</v>
+      </c>
+      <c r="F112" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>273</v>
+      </c>
+      <c r="B113">
+        <v>86</v>
+      </c>
+      <c r="C113" t="s">
+        <v>257</v>
+      </c>
+      <c r="D113" t="s">
+        <v>140</v>
+      </c>
+      <c r="F113" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>274</v>
+      </c>
+      <c r="B114">
+        <v>87</v>
+      </c>
+      <c r="C114" t="s">
+        <v>166</v>
+      </c>
+      <c r="D114" t="s">
+        <v>140</v>
+      </c>
+      <c r="F114" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>275</v>
+      </c>
+      <c r="B115">
+        <v>88</v>
+      </c>
+      <c r="C115" t="s">
+        <v>166</v>
+      </c>
+      <c r="D115" t="s">
+        <v>140</v>
+      </c>
+      <c r="F115" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>276</v>
+      </c>
+      <c r="B116">
+        <v>89</v>
+      </c>
+      <c r="C116" t="s">
+        <v>261</v>
+      </c>
+      <c r="D116" t="s">
+        <v>140</v>
+      </c>
+      <c r="F116" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>277</v>
+      </c>
+      <c r="B117">
+        <v>90</v>
+      </c>
+      <c r="C117" t="s">
+        <v>263</v>
+      </c>
+      <c r="D117" t="s">
+        <v>140</v>
+      </c>
+      <c r="F117" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>278</v>
+      </c>
+      <c r="B118">
+        <v>5</v>
+      </c>
+      <c r="C118" t="s">
+        <v>7</v>
+      </c>
+      <c r="D118" t="s">
+        <v>265</v>
+      </c>
+      <c r="E118" t="s">
+        <v>9</v>
+      </c>
+      <c r="F118" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>279</v>
+      </c>
+      <c r="B119">
+        <v>1</v>
+      </c>
+      <c r="C119" t="s">
+        <v>267</v>
+      </c>
+      <c r="D119" t="s">
+        <v>268</v>
+      </c>
+      <c r="E119" t="s">
+        <v>9</v>
+      </c>
+      <c r="F119" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>280</v>
+      </c>
+      <c r="B120">
+        <v>2</v>
+      </c>
+      <c r="C120" t="s">
+        <v>270</v>
+      </c>
+      <c r="D120" t="s">
+        <v>26</v>
+      </c>
+      <c r="E120" t="s">
+        <v>271</v>
+      </c>
+      <c r="F120" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>281</v>
+      </c>
+      <c r="B121">
+        <v>35</v>
+      </c>
+      <c r="C121" t="s">
+        <v>156</v>
+      </c>
+      <c r="D121" t="s">
+        <v>273</v>
+      </c>
+      <c r="F121" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>
